--- a/member_deposit/2026-09-08_会员沉淀分析.xlsx
+++ b/member_deposit/2026-09-08_会员沉淀分析.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,163 +448,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25426</v>
+        <v>566</v>
       </c>
       <c r="C2" t="n">
-        <v>25426</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+        <v>566</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-54429</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>25426</v>
+        <v>54995</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27959</v>
+        <v>158</v>
       </c>
       <c r="C3" t="n">
-        <v>27958</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
+        <v>158</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-17890</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>27959</v>
+        <v>18048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>（未匹配门店）</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54995</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>54991</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>54995</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>+26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74109</v>
+        <v>45</v>
       </c>
       <c r="C5" t="n">
-        <v>74108</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-11845</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>74109</v>
+        <v>11890</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10809</v>
+        <v>795</v>
       </c>
       <c r="C6" t="n">
-        <v>10809</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10809</v>
-      </c>
+        <v>795</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>剔除-门店标记剔除（不计入）</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18048</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18048</v>
-      </c>
-      <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="n">
-        <v>18048</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>未消费会员</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>11890</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11811</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11890</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>223236</v>
-      </c>
-      <c r="C9" t="n">
-        <v>223151</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>剔除-门店标记剔除（不计入）</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>13265</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -617,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +579,36 @@
         <is>
           <t>记录数</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>华为宁德霞浦方圆荟</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>华为宁德古田中央名城</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>华为宁德霞浦太康路二店</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,16 +650,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DJI上海徐汇万科广场授权体验店</t>
+          <t>华为北京丰台鑫嘉汇</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -689,16 +668,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DJI上海FFC滨江悅里授权体验店</t>
+          <t>华为北京同成街华联</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -707,16 +686,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>华为北京上德银泰</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -725,16 +704,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>华为北京回龙观一店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>208</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -743,16 +722,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>上海爱飞</t>
+          <t>北京易联</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>华为北京房山燕隆汇</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>516</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -761,16 +740,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>华为北京常营龙湖</t>
+          <t>华为厦门思明大西洋天虹</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -779,16 +758,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APR北京昌发展万科</t>
+          <t>华为福州宜家荟聚</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>268</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
@@ -797,16 +776,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APR北京北苑龙湖</t>
+          <t>华为厦门思明加州广场</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -815,16 +794,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APR北京大红门银泰</t>
+          <t>华为福州仓山爱琴海</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -833,378 +812,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>北京中恒</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APR北京大峡谷凯德茂</t>
+          <t>华为福州砂之船奥莱</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>344</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>华为北京回龙观一店</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>292</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>华为北京京投小站</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>330</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>华为北京上德银泰</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>418</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>华为北京同成街华联</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>443</v>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>北京易联</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>华为北京房山燕隆汇</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>501</v>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DJI北京双安商场授权体验店</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>71</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DJI北京北投新奥天虹授权体验店</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>343</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DJI北京龙湖长安天街授权体验店</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>407</v>
-      </c>
-      <c r="D19" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DJI北京万柳华联授权体验店</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>451</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>北京飞航</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DJI北京龙湖熙悦天街授权体验店</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>522</v>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>APR成都凯德魅力城</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>99</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>APR成都东安天街</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>110</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>APR成都天府环宇坊</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>121</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>（旧）APR成都凯德魅力城</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>133</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>四川新跃</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>APR成都环球中心</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>156</v>
-      </c>
-      <c r="D26" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>华为厦门思明星河COCO Park</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>40</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>华为厦门湖里江头</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>144</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>华为福州福清高山</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>145</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>华为厦门思明大西洋天虹</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>181</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>华为厦门思明君尚天虹</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>225</v>
-      </c>
-      <c r="D31" t="n">
         <v>5</v>
       </c>
     </row>
